--- a/data/dividends_info_20260819.xlsx
+++ b/data/dividends_info_20260819.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>44.78499984741211</v>
+        <v>43.88999938964844</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2009601435896859</v>
+        <v>0.2050581026465603</v>
       </c>
       <c r="J2" t="n">
         <v>208</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>67.25</v>
+        <v>67.34999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.04089219330855</v>
+        <v>1.039346719909684</v>
       </c>
       <c r="J3" t="n">
         <v>187</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.100000381469727</v>
+        <v>9.260000228881836</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6593406317012648</v>
+        <v>0.6479481481313648</v>
       </c>
       <c r="J4" t="n">
         <v>117</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.4699999988079071</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I5" t="n">
-        <v>0.851063831945845</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J5" t="n">
         <v>117</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>44.79000091552734</v>
+        <v>43.88999938964844</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2009377052028586</v>
+        <v>0.2050581026465603</v>
       </c>
       <c r="J6" t="n">
         <v>117</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.109999895095825</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="I7" t="n">
-        <v>3.649289280960038</v>
+        <v>3.719806883248261</v>
       </c>
       <c r="J7" t="n">
         <v>96</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>24.17499923706055</v>
+        <v>23.93000030517578</v>
       </c>
       <c r="I8" t="n">
-        <v>1.116856291710185</v>
+        <v>1.128290833918636</v>
       </c>
       <c r="J8" t="n">
         <v>96</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.04999923706055</v>
+        <v>22.76000022888184</v>
       </c>
       <c r="I9" t="n">
-        <v>2.559653013139274</v>
+        <v>2.592267109256465</v>
       </c>
       <c r="J9" t="n">
         <v>96</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.769999980926514</v>
+        <v>5.739999771118164</v>
       </c>
       <c r="I10" t="n">
-        <v>3.466204517523849</v>
+        <v>3.484320696428174</v>
       </c>
       <c r="J10" t="n">
         <v>89</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.09000015258789</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="I11" t="n">
-        <v>4.558969207567543</v>
+        <v>4.479065038913997</v>
       </c>
       <c r="J11" t="n">
         <v>68</v>
@@ -992,8 +992,12 @@
           <t>IT0005359101</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>7.650000095367432</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7843137157126817</v>
+      </c>
       <c r="J12" t="n">
         <v>61</v>
       </c>
@@ -1036,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.4659999907016754</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8583691158399027</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J13" t="n">
         <v>61</v>
@@ -1177,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>24.17499923706055</v>
+        <v>23.93000030517578</v>
       </c>
       <c r="I16" t="n">
-        <v>1.116856291710185</v>
+        <v>1.128290833918636</v>
       </c>
       <c r="J16" t="n">
         <v>33</v>
@@ -1224,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.955000042915344</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>2.915600959015848</v>
+        <v>2.85</v>
       </c>
       <c r="J17" t="n">
         <v>33</v>
@@ -1271,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>44.79000091552734</v>
+        <v>43.88999938964844</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2009377052028586</v>
+        <v>0.2050581026465603</v>
       </c>
       <c r="J18" t="n">
         <v>33</v>
@@ -1318,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>92.75</v>
+        <v>91</v>
       </c>
       <c r="I19" t="n">
-        <v>1.433962264150943</v>
+        <v>1.461538461538462</v>
       </c>
       <c r="J19" t="n">
         <v>33</v>
@@ -1365,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5.860000133514404</v>
+        <v>5.820000171661377</v>
       </c>
       <c r="I20" t="n">
-        <v>5.119453808272897</v>
+        <v>5.154639023221232</v>
       </c>
       <c r="J20" t="n">
         <v>26</v>
@@ -1412,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.4659999907016754</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8583691158399027</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J21" t="n">
         <v>5</v>
@@ -1459,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.480000019073486</v>
+        <v>2.460000038146973</v>
       </c>
       <c r="I22" t="n">
-        <v>8.870967673709565</v>
+        <v>8.943089292214722</v>
       </c>
       <c r="J22" t="n">
         <v>-9</v>
@@ -1647,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>5.96999979019165</v>
+        <v>5.940000057220459</v>
       </c>
       <c r="I26" t="n">
-        <v>4.187604837285504</v>
+        <v>4.208754168210969</v>
       </c>
       <c r="J26" t="n">
         <v>-23</v>
@@ -1694,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4.21999979019165</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="I27" t="n">
-        <v>3.317535709963671</v>
+        <v>3.286384799954511</v>
       </c>
       <c r="J27" t="n">
         <v>-30</v>
@@ -1741,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>9.508000373840332</v>
+        <v>9.475000381469727</v>
       </c>
       <c r="I28" t="n">
-        <v>2.734539227778602</v>
+        <v>2.74406321406047</v>
       </c>
       <c r="J28" t="n">
         <v>-30</v>
@@ -1788,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>13.85999965667725</v>
+        <v>13.89999961853027</v>
       </c>
       <c r="I29" t="n">
-        <v>4.329004436237065</v>
+        <v>4.316546881052659</v>
       </c>
       <c r="J29" t="n">
         <v>-30</v>
@@ -1835,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2.677999973297119</v>
+        <v>2.667999982833862</v>
       </c>
       <c r="I30" t="n">
-        <v>8.215085966903086</v>
+        <v>8.245877114523935</v>
       </c>
       <c r="J30" t="n">
         <v>-30</v>
@@ -1882,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.4659999907016754</v>
+        <v>0.4779999852180481</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8583691158399027</v>
+        <v>0.8368201095603234</v>
       </c>
       <c r="J31" t="n">
         <v>-30</v>
@@ -1929,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>6.53000020980835</v>
+        <v>6.570000171661377</v>
       </c>
       <c r="I32" t="n">
-        <v>3.675344445464326</v>
+        <v>3.652967941084702</v>
       </c>
       <c r="J32" t="n">
         <v>-30</v>
@@ -3437,61 +3441,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DigiTouch S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>DigiTouch S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>